--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/WYOMING_2022.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/WYOMING_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D263"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C4">
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Ascensión</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Bachíniva</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Balleza</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Bocoyna</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Dr. Belisario Domínguez</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -670,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C23">
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -696,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C25">
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Julimes</t>
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>La Cruz</t>
@@ -761,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -774,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Maguarichi</t>
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -800,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Meoqui</t>
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Ojinaga</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -865,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Santa Bárbara</t>
@@ -878,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Temósachic</t>
@@ -891,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Valle de Zaragoza</t>
+          <t>Valle De Zaragoza</t>
         </is>
       </c>
       <c r="C40">
@@ -904,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -961,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1020,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1036,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1049,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1062,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1075,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1088,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1114,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1127,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>General Simón Bolívar</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1210,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Guanaceví</t>
@@ -1223,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Indé</t>
@@ -1236,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1249,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -1262,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Nazas</t>
@@ -1275,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1288,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -1301,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -1314,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1327,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1342,7 +1657,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1358,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1371,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C75">
@@ -1384,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C76">
@@ -1397,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1410,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C78">
@@ -1423,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C79">
@@ -1436,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Tianguistenco</t>
@@ -1449,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C81">
@@ -1462,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1475,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -1488,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Villa de Allende</t>
+          <t>Villa De Allende</t>
         </is>
       </c>
       <c r="C84">
@@ -1501,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Villa del Carbón</t>
+          <t>Villa Del Carbón</t>
         </is>
       </c>
       <c r="C85">
@@ -1514,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>León</t>
@@ -1571,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1584,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C91">
@@ -1597,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -1610,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C93">
@@ -1623,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -1636,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1656,7 +2076,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C96">
@@ -1667,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C97">
@@ -1680,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -1693,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C99">
@@ -1706,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C100">
@@ -1719,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -1732,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -1745,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -1758,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1789,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1802,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -1815,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C108">
@@ -1828,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -1841,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -1854,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1885,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Chimaltitán</t>
@@ -1898,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1911,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -1924,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1937,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -1950,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C118">
@@ -1963,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C119">
@@ -1976,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C120">
@@ -1989,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -2002,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C122">
@@ -2015,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Sayula</t>
@@ -2028,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C124">
@@ -2041,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -2054,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2067,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C127">
@@ -2080,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Villa Corona</t>
@@ -2093,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2106,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C130">
@@ -2119,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -2132,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2163,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -2176,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Ixtlán</t>
@@ -2189,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -2202,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>José Sixto Verduzco</t>
@@ -2215,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2228,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -2241,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -2254,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -2267,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -2280,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -2293,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Tlalpujahua</t>
@@ -2306,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2319,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2332,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2363,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -2376,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C150">
@@ -2389,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2420,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Del Nayar</t>
@@ -2433,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C154">
@@ -2446,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Jala</t>
@@ -2459,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -2472,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2485,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2505,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C159">
@@ -2516,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C160">
@@ -2529,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>San Juan Mazatlán</t>
@@ -2542,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>San Pablo Cuatro Venados</t>
@@ -2555,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>San Sebastián Tecomaxtlahuaca</t>
@@ -2568,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -2581,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Santa María Ozolotepec</t>
@@ -2594,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Santa María Zoquitlán</t>
@@ -2607,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -2620,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -2633,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C169">
@@ -2646,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2677,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -2690,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -2703,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -2716,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -2729,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2742,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -2755,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -2768,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Santo Tomás Hueyotlipan</t>
@@ -2781,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -2794,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -2807,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C182">
@@ -2820,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Tlapacoya</t>
@@ -2833,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -2846,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Zongozotla</t>
@@ -2859,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2890,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Peñamiller</t>
@@ -2903,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C189">
@@ -2916,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C190">
@@ -2929,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2960,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C193">
@@ -2973,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -2986,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -2999,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C196">
@@ -3012,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -3025,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3056,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -3069,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -3082,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -3095,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -3108,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -3121,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3152,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Bácum</t>
@@ -3165,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Bavispe</t>
@@ -3178,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -3191,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -3204,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3235,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3266,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3297,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -3310,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -3323,9 +4283,14 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Contla de Juan Cuamatzi</t>
+          <t>Contla De Juan Cuamatzi</t>
         </is>
       </c>
       <c r="C219">
@@ -3336,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Cuaxomulco</t>
@@ -3349,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -3362,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -3375,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Muñoz de Domingo Arenas</t>
+          <t>Muñoz De Domingo Arenas</t>
         </is>
       </c>
       <c r="C223">
@@ -3388,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>San Lucas Tecopilco</t>
@@ -3401,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Tetlatlahuca</t>
@@ -3414,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -3427,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -3440,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Tzompantepec</t>
@@ -3453,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -3466,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Xicohtzinco</t>
@@ -3479,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Yauhquemehcan</t>
@@ -3492,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3523,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -3536,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -3549,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -3562,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -3575,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -3588,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -3601,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Tenochtitlán</t>
@@ -3614,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Tlaquilpa</t>
@@ -3627,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -3640,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -3653,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3684,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -3697,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -3710,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -3723,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -3736,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Tepetongo</t>
@@ -3749,9 +4859,14 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C251">
@@ -3762,9 +4877,14 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Trinidad García de la Cadena</t>
+          <t>Trinidad García De La Cadena</t>
         </is>
       </c>
       <c r="C252">
@@ -3775,9 +4895,14 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C253">
@@ -3788,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -3801,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -3814,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3837,41 +4977,6 @@
       </c>
       <c r="D257">
         <v>1</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
